--- a/docs/45Flow-Premium-Test-Plan-Linux.xlsx
+++ b/docs/45Flow-Premium-Test-Plan-Linux.xlsx
@@ -670,7 +670,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>1. Installation (Linux)</t>
+          <t>01. Installation (Linux)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -706,7 +706,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>1. Installation (Linux)</t>
+          <t>01. Installation (Linux)</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>1. Installation (Linux)</t>
+          <t>01. Installation (Linux)</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -776,7 +776,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>1. Installation (Linux)</t>
+          <t>01. Installation (Linux)</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -810,7 +810,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>1. Installation (Linux)</t>
+          <t>01. Installation (Linux)</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>1. Installation (Linux)</t>
+          <t>01. Installation (Linux)</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>1. Installation (Linux)</t>
+          <t>01. Installation (Linux)</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>5. Local Upload (Linux)</t>
+          <t>05. Local Upload (Linux)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>5. Local Upload (Linux)</t>
+          <t>05. Local Upload (Linux)</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>5. Local Upload (Linux)</t>
+          <t>05. Local Upload (Linux)</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1016,7 +1016,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>5. Local Upload (Linux)</t>
+          <t>05. Local Upload (Linux)</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1254,7 +1254,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2. Server Connection &amp; Auth</t>
+          <t>02. Server Connection &amp; Auth</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>2. Server Connection &amp; Auth</t>
+          <t>02. Server Connection &amp; Auth</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -1322,7 +1322,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2. Server Connection &amp; Auth</t>
+          <t>02. Server Connection &amp; Auth</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>2. Server Connection &amp; Auth</t>
+          <t>02. Server Connection &amp; Auth</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -1392,7 +1392,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2. Server Connection &amp; Auth</t>
+          <t>02. Server Connection &amp; Auth</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>2. Server Connection &amp; Auth</t>
+          <t>02. Server Connection &amp; Auth</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -1461,7 +1461,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2. Server Connection &amp; Auth</t>
+          <t>02. Server Connection &amp; Auth</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -1495,7 +1495,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2. Server Connection &amp; Auth</t>
+          <t>02. Server Connection &amp; Auth</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -1528,7 +1528,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2. Server Connection &amp; Auth</t>
+          <t>02. Server Connection &amp; Auth</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -1562,7 +1562,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3. Dashboard &amp; Navigation</t>
+          <t>03. Dashboard &amp; Navigation</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -1595,7 +1595,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>3. Dashboard &amp; Navigation</t>
+          <t>03. Dashboard &amp; Navigation</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -1627,7 +1627,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>3. Dashboard &amp; Navigation</t>
+          <t>03. Dashboard &amp; Navigation</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -1660,7 +1660,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>4. File Share Links</t>
+          <t>04. File Share Links</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -1698,7 +1698,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>4. File Share Links</t>
+          <t>04. File Share Links</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -1734,7 +1734,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>4. File Share Links</t>
+          <t>04. File Share Links</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -1771,7 +1771,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>4. File Share Links</t>
+          <t>04. File Share Links</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -1809,7 +1809,7 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>5. Local Upload</t>
+          <t>05. Local Upload</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -1847,7 +1847,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>5. Local Upload</t>
+          <t>05. Local Upload</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -1882,7 +1882,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>5. Local Upload</t>
+          <t>05. Local Upload</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>6. Upload Links</t>
+          <t>06. Upload Links</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -1951,7 +1951,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>6. Upload Links</t>
+          <t>06. Upload Links</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -1986,7 +1986,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>7. Transfer Dock</t>
+          <t>07. Transfer Dock</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>7. Transfer Dock</t>
+          <t>07. Transfer Dock</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -2053,7 +2053,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>7. Transfer Dock</t>
+          <t>07. Transfer Dock</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>8. Managing Links</t>
+          <t>08. Managing Links</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -2120,7 +2120,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>8. Managing Links</t>
+          <t>08. Managing Links</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -2154,7 +2154,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>8. Managing Links</t>
+          <t>08. Managing Links</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -2187,7 +2187,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>8. Managing Links</t>
+          <t>08. Managing Links</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -2219,7 +2219,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>9. Video Player &amp; Review</t>
+          <t>09. Video Player &amp; Review</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -2252,7 +2252,7 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>9. Video Player &amp; Review</t>
+          <t>09. Video Player &amp; Review</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -2285,7 +2285,7 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>9. Video Player &amp; Review</t>
+          <t>09. Video Player &amp; Review</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -2321,7 +2321,7 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>9. Video Player &amp; Review</t>
+          <t>09. Video Player &amp; Review</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
